--- a/output/EIRL ADVANCED LOGISTICS GROUP (ALG).xlsx
+++ b/output/EIRL ADVANCED LOGISTICS GROUP (ALG).xlsx
@@ -1019,6 +1019,11 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NAM8573436</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>34851</t>
@@ -1027,6 +1032,26 @@
       <c r="D12" t="inlineStr">
         <is>
           <t>01-118-1-2026- 1868</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>USNYC</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>26/07/2026 23:32:38</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>22/07/2026 17:36:15</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>26/07/2026 23:32:48</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1039,6 +1064,11 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NAM8548922</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>34851</t>
@@ -1047,6 +1077,26 @@
       <c r="D13" t="inlineStr">
         <is>
           <t>01-118-1-2026- 1868</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>USNYC</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>26/07/2026 23:41:15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>22/07/2026 17:36:15</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>26/07/2026 23:41:24</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1059,6 +1109,11 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SHZ8109349</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>35335</t>
@@ -1067,6 +1122,26 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>01-118-1-2026- 1981</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>24/07/2026 15:23:20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>29/07/2026 23:42:09</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>30/07/2026 00:04:23</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1079,6 +1154,11 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HLCUTS12605CEXA9</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>35924</t>
@@ -1087,6 +1167,26 @@
       <c r="D15" t="inlineStr">
         <is>
           <t>01-118-1-2026- 2022</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30/07/2026 17:17:26</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>02/08/2026 16:15:17</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>02/08/2026 16:23:37</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1099,6 +1199,11 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HLCUNG1260641526</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>36421</t>
@@ -1107,6 +1212,26 @@
       <c r="D16" t="inlineStr">
         <is>
           <t>01-118-1-2026- 1988</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>24/07/2026 10:52:52</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>04/08/2026 14:53:59</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>04/08/2026 15:05:56</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">

--- a/output/EIRL ADVANCED LOGISTICS GROUP (ALG).xlsx
+++ b/output/EIRL ADVANCED LOGISTICS GROUP (ALG).xlsx
@@ -1527,7 +1527,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-43470627</t>
+          <t>2026-43464373</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-43456475</t>
+          <t>2026-43470627</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-43464373</t>
+          <t>2026-43456475</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-42860973</t>
+          <t>2026-42862348</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-42862348</t>
+          <t>2026-42860973</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-48585700</t>
+          <t>2026-48588019</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-48588019</t>
+          <t>2026-48585700</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
